--- a/results/0916-all/陇中青东丘陵农牧区/tech_selected_summary.xlsx
+++ b/results/0916-all/陇中青东丘陵农牧区/tech_selected_summary.xlsx
@@ -175,133 +175,133 @@
     <t>庄浪县</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>技术25</t>
-  </si>
-  <si>
-    <t>技术26</t>
-  </si>
-  <si>
-    <t>技术27</t>
-  </si>
-  <si>
-    <t>技术28</t>
-  </si>
-  <si>
-    <t>技术29</t>
-  </si>
-  <si>
-    <t>技术30</t>
-  </si>
-  <si>
-    <t>技术31</t>
-  </si>
-  <si>
-    <t>技术32</t>
-  </si>
-  <si>
-    <t>技术33</t>
-  </si>
-  <si>
-    <t>技术34</t>
-  </si>
-  <si>
-    <t>技术35</t>
-  </si>
-  <si>
-    <t>技术36</t>
-  </si>
-  <si>
-    <t>技术37</t>
-  </si>
-  <si>
-    <t>技术38</t>
-  </si>
-  <si>
-    <t>技术39</t>
-  </si>
-  <si>
-    <t>技术40</t>
-  </si>
-  <si>
-    <t>技术41</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Tech25</t>
+  </si>
+  <si>
+    <t>Tech26</t>
+  </si>
+  <si>
+    <t>Tech27</t>
+  </si>
+  <si>
+    <t>Tech28</t>
+  </si>
+  <si>
+    <t>Tech29</t>
+  </si>
+  <si>
+    <t>Tech30</t>
+  </si>
+  <si>
+    <t>Tech31</t>
+  </si>
+  <si>
+    <t>Tech32</t>
+  </si>
+  <si>
+    <t>Tech33</t>
+  </si>
+  <si>
+    <t>Tech34</t>
+  </si>
+  <si>
+    <t>Tech35</t>
+  </si>
+  <si>
+    <t>Tech36</t>
+  </si>
+  <si>
+    <t>Tech37</t>
+  </si>
+  <si>
+    <t>Tech38</t>
+  </si>
+  <si>
+    <t>Tech39</t>
+  </si>
+  <si>
+    <t>Tech40</t>
+  </si>
+  <si>
+    <t>Tech41</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
@@ -310,10 +310,10 @@
     <t>EEF(NI)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 5544962.77</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
+    <t>5544962.77</t>
+  </si>
+  <si>
+    <t>0.00</t>
   </si>
   <si>
     <t>Increasing feeding level_sheep &amp; goat</t>
@@ -427,28 +427,28 @@
     <t>irrigation (drip irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 36515311.61</t>
-  </si>
-  <si>
-    <t>总经济成本: 1484705.15</t>
-  </si>
-  <si>
-    <t>总经济成本: 300159.50</t>
+    <t>36515311.61</t>
+  </si>
+  <si>
+    <t>1484705.15</t>
+  </si>
+  <si>
+    <t>300159.50</t>
   </si>
   <si>
     <t>rolller press_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 1054490.50</t>
+    <t>1054490.50</t>
   </si>
   <si>
     <t>Plant-derived N substitution_maize</t>
   </si>
   <si>
-    <t>总经济成本: 118149354.81</t>
-  </si>
-  <si>
-    <t>总经济成本: 2220617.26</t>
+    <t>118149354.81</t>
+  </si>
+  <si>
+    <t>2220617.26</t>
   </si>
   <si>
     <t>Zeolite_Poultry</t>
@@ -457,34 +457,34 @@
     <t>Frequent removal_poultry</t>
   </si>
   <si>
-    <t>总经济成本: 18089281.77</t>
-  </si>
-  <si>
-    <t>总经济成本: 6176089.66</t>
-  </si>
-  <si>
-    <t>总经济成本: 3768772.76</t>
+    <t>18089281.77</t>
+  </si>
+  <si>
+    <t>6176089.66</t>
+  </si>
+  <si>
+    <t>3768772.76</t>
   </si>
   <si>
     <t>Organic acid_sheep &amp; goat</t>
   </si>
   <si>
-    <t>总经济成本: 2212642.50</t>
+    <t>2212642.50</t>
   </si>
   <si>
     <t>irrigation (water-saving irrigation)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 4208759.66</t>
+    <t>4208759.66</t>
   </si>
   <si>
     <t>incorporation_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 513844.20</t>
-  </si>
-  <si>
-    <t>总经济成本: 1789348.16</t>
+    <t>513844.20</t>
+  </si>
+  <si>
+    <t>1789348.16</t>
   </si>
 </sst>
 </file>
